--- a/LULU/model18unaltered.xlsx
+++ b/LULU/model18unaltered.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/LULU/model18unaltered.xlsx
+++ b/LULU/model18unaltered.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1276,7 +1276,7 @@
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1992,7 +1992,7 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -5820,10 +5820,10 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8159,7 +8159,7 @@
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -9509,7 +9509,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" hidden="1" outlineLevel="1" ht="28" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -9798,7 +9798,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M104"/>
@@ -9806,7 +9806,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -9815,8 +9815,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="12" max="12"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -12503,7 +12503,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>

--- a/LULU/model18unaltered.xlsx
+++ b/LULU/model18unaltered.xlsx
@@ -1115,13 +1115,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1129,6 +1130,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1143,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1150,6 +1153,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1178,6 +1182,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -1207,6 +1212,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1246,12 +1252,9 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Built from scratch for the GIS IR selection assignment.</t>
-        </is>
-      </c>
+      <c r="B25" s="11" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/LULU/model18unaltered.xlsx
+++ b/LULU/model18unaltered.xlsx
@@ -1198,19 +1198,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>ASSUMPTIONS GUIDE (PDF — every tab)</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>LULU_Assumptions_Memo.pdf — full guide: every red assumption on WACC, Scenarios, Revenue Drivers, NOPAT Bridge, DCF, Comps &amp; 3-Statement
-Ctrl+F: Open for justification, clickable source links, and Ctrl+F proof for every assumption.</t>
-        </is>
-      </c>
+      <c r="B17" s="10" t="n"/>
     </row>
     <row r="18"/>
     <row r="19">
@@ -1258,11 +1249,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1392,6 +1382,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1543,6 +1534,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1849,6 +1841,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1892,6 +1885,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2672,6 +2666,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4674,6 +4669,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4731,6 +4727,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4738,6 +4735,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -6638,6 +6636,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -7197,6 +7196,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7436,6 +7436,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7851,6 +7852,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -8249,6 +8251,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8527,6 +8530,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -9554,6 +9558,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -9923,12 +9928,7 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
-        <is>
-          <t>Full Assumptions Guide (PDF)
-Ctrl+F: Every red assumption on every tab — justification, source link, Ctrl+F proof.</t>
-        </is>
-      </c>
+      <c r="A4" s="38" t="n"/>
       <c r="C4" s="85" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab
@@ -11342,6 +11342,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -11612,6 +11613,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -11630,6 +11633,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -11690,6 +11694,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -11774,6 +11779,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -11894,6 +11900,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -11954,6 +11961,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -12045,6 +12053,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -12163,6 +12172,8 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -12429,67 +12440,66 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink ref="C4" location="'NOPAT Bridge'!A1"/>
     <hyperlink ref="D4" location="'Revenue Drivers'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId33"/>
     <hyperlink ref="C30" location="'Scenarios'!A105"/>
     <hyperlink ref="C31" location="'Scenarios'!A110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId35"/>
     <hyperlink ref="C33" location="'Scenarios'!A120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId44"/>
     <hyperlink ref="C82" location="'DCF'!E46"/>
     <hyperlink ref="M82" location="'Comps'!A45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId45"/>
     <hyperlink ref="L98" location="'Scenarios'!G10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId46"/>
     <hyperlink ref="L99" location="'WACC'!E41"/>
     <hyperlink ref="L100" location="'WACC'!E41"/>
     <hyperlink ref="L101" location="'WACC'!E41"/>
     <hyperlink ref="L102" location="'WACC'!E41"/>
     <hyperlink ref="L103" location="'WACC'!E41"/>
     <hyperlink ref="C104" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12703,6 +12713,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -13120,6 +13131,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -13240,6 +13252,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -13306,6 +13319,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -13395,6 +13409,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -13577,6 +13592,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>
